--- a/data/The_Print_Planet_Products_Catalog_Client_Editable.xlsx
+++ b/data/The_Print_Planet_Products_Catalog_Client_Editable.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Products Catalog (Editable)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Categories Reference" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Instructions &amp; Import Guide" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Products &amp; Images" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Categories" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,17 +36,6 @@
       <name val="Calibri"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="0017365D"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -55,6 +43,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00217A4B"/>
+        <bgColor rgb="00217A4B"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -70,14 +64,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00217A4B"/>
-        <bgColor rgb="00217A4B"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FDF2E9"/>
-        <bgColor rgb="00FDF2E9"/>
+        <fgColor rgb="00FEF5E7"/>
+        <bgColor rgb="00FEF5E7"/>
       </patternFill>
     </fill>
   </fills>
@@ -107,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -119,10 +107,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -133,12 +121,9 @@
     <xf numFmtId="4" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -213,6 +198,1586 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>11</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId17"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId18"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId20"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="21" name="Image 21" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId21"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="22" name="Image 22" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId22"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="23" name="Image 23" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId23"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="24" name="Image 24" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId24"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>25</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="25" name="Image 25" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId25"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>26</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="26" name="Image 26" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId26"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="27" name="Image 27" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId27"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>28</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="28" name="Image 28" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId28"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="29" name="Image 29" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="30" name="Image 30" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="31" name="Image 31" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="32" name="Image 32" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId32"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId33"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>34</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId34"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>35</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId35"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>36</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId36"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId37"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>38</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId38"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId39"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId40"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId41"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>42</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId42"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId43"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId44"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId45"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>46</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId46"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>47</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId47"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>48</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId48"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>49</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId54"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId55"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId56"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId57"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId58"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId59"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId60"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId61"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId62"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="619125" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId63"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,198 +2069,200 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S64"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="45" customWidth="1" min="9" max="9"/>
-    <col width="37" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="38" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="10" max="10"/>
+    <col width="37" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="45" customWidth="1" min="15" max="15"/>
     <col width="45" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="29" customWidth="1" min="18" max="18"/>
-    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
+    <col width="27" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Product Image</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Product Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Category Name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Category Slug</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Trade Price (INR)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Display Price Text</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>MOQ</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Dimensions</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Color</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Image Filename</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Image URL</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Featured (Yes/No)</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Short Description</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Specifications (JSON)</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Client Revised Name</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Client Revised Price (INR)</t>
         </is>
       </c>
-      <c r="S1" s="3" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Client New Image Link / File</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Client Notes / Revisions</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="4" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>LAN-YEL-16M</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>16 mm  Indian Yellow Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="F2" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="4" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="K2" s="4" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>LAN-YEL-16M.png</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-YEL-16M.png</t>
         </is>
       </c>
-      <c r="M2" s="4" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="4" t="inlineStr">
         <is>
           <t>16 mm  Indian Yellow Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16 mm  Indian Yellow Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="P2" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Yellow", "Material": "Polyester"}</t>
         </is>
@@ -703,78 +2270,75 @@
       <c r="Q2" s="7" t="inlineStr"/>
       <c r="R2" s="8" t="inlineStr"/>
       <c r="S2" s="7" t="inlineStr"/>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="T2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="60" customHeight="1">
+      <c r="A3" s="4" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>LAN-RED-16M</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>16 mm Indian Red Color Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>LAN-RED-16M.png</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-RED-16M.png</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>16 mm Indian Red Color Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16 mm Indian Red Color Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Red", "Material": "Polyester"}</t>
         </is>
@@ -782,78 +2346,75 @@
       <c r="Q3" s="7" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="7" t="inlineStr"/>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="T3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="60" customHeight="1">
+      <c r="A4" s="4" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>LAN-BLA-16M</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Black Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>LAN-BLA-16M.png</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-BLA-16M.png</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Black Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16MM Indian Black Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Black", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -861,78 +2422,75 @@
       <c r="Q4" s="7" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="7" t="inlineStr"/>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="T4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>LAN-ORA-16M</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Orange Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>270</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>₹ 270 / Roll</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>LAN-ORA-16M.png</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-ORA-16M.png</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Orange Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16MM Indian Orange Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Orange", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -940,78 +2498,75 @@
       <c r="Q5" s="7" t="inlineStr"/>
       <c r="R5" s="8" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="T5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>LAN-PUR-16M</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Purple Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>280</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>₹ 280 / Roll</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>LAN-PUR-16M.png</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-PUR-16M.png</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Purple Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16MM Indian Purple Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="P6" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1019,78 +2574,75 @@
       <c r="Q6" s="7" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="7" t="inlineStr"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="T6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>LAN-ROY-16M</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Royal Blue Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>16 mm</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Royal Blue</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>LAN-ROY-16M.png</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-ROY-16M.png</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>16MM Indian Royal Blue Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16MM Indian Royal Blue Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="P7" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "16 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1098,78 +2650,75 @@
       <c r="Q7" s="7" t="inlineStr"/>
       <c r="R7" s="8" t="inlineStr"/>
       <c r="S7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="T7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>LAN-ORA-20M</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>20 MM Indian Orange Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>Orange</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>LAN-ORA-20M.png</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-ORA-20M.png</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>20 MM Indian Orange Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20 MM Indian Orange Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Orange", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1177,78 +2726,75 @@
       <c r="Q8" s="7" t="inlineStr"/>
       <c r="R8" s="8" t="inlineStr"/>
       <c r="S8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="T8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9" ht="60" customHeight="1">
+      <c r="A9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>LAN-PUR-20M</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Purple Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="F9" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Purple</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>LAN-PUR-20M.png</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-PUR-20M.png</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Purple Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20MM Indian Purple Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1256,78 +2802,75 @@
       <c r="Q9" s="7" t="inlineStr"/>
       <c r="R9" s="8" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="T9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>LAN-RED-20M</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Red Color Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="F10" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>LAN-RED-20M.png</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-RED-20M.png</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Red Color Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20MM Indian Red Color Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Material": "Polyester"}</t>
         </is>
@@ -1335,78 +2878,75 @@
       <c r="Q10" s="7" t="inlineStr"/>
       <c r="R10" s="8" t="inlineStr"/>
       <c r="S10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="T10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>LAN-ROY-20M</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Royal Blue Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="F11" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Royal Blue</t>
         </is>
       </c>
-      <c r="K11" s="4" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>LAN-ROY-20M.png</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-ROY-20M.png</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Royal Blue Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20MM Indian Royal Blue Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1414,78 +2954,75 @@
       <c r="Q11" s="7" t="inlineStr"/>
       <c r="R11" s="8" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="T11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="4" t="inlineStr"/>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>LAN-YEL-20M</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Yellow Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n">
+      <c r="F12" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Yellow</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>LAN-YEL-20M.png</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-YEL-20M.png</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>20MM Indian Yellow Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20MM Indian Yellow Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Yellow", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1493,78 +3030,75 @@
       <c r="Q12" s="7" t="inlineStr"/>
       <c r="R12" s="8" t="inlineStr"/>
       <c r="S12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="T12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="inlineStr"/>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>LAN-BLA-20M</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>20mm  Indian BLACK Colour Satin Lanyard Roll</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n">
+      <c r="F13" s="6" t="n">
         <v>300</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>₹ 300 / Roll</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>20 mm</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Black</t>
         </is>
       </c>
-      <c r="K13" s="4" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>LAN-BLA-20M.png</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-BLA-20M.png</t>
         </is>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>20mm  Indian BLACK Colour Satin Lanyard Roll - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20mm  Indian BLACK Colour Satin Lanyard Roll manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
         <is>
           <t>{"Roll Length": "100 m", "Lanyard Width": "20 mm", "Printing Type": "Screen Print", "Core Type": "Plastic Core", "Usage": "Lanyard Making", "Color": "Black", "Roll Packing": "Single Roll", "Material": "Polyester"}</t>
         </is>
@@ -1572,64 +3106,61 @@
       <c r="Q13" s="7" t="inlineStr"/>
       <c r="R13" s="8" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="T13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>HLD-C2T</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>C2T ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="5" t="inlineStr"/>
-      <c r="G14" s="5" t="inlineStr"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
-      <c r="K14" s="4" t="inlineStr">
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>HLD-C2T.png</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-C2T.png</t>
         </is>
       </c>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>C2T ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade C2T ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="P14" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -1637,64 +3168,61 @@
       <c r="Q14" s="7" t="inlineStr"/>
       <c r="R14" s="8" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="T14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>HLD-H2T</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>H2T ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="5" t="inlineStr"/>
-      <c r="G15" s="5" t="inlineStr"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="4" t="inlineStr">
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>HLD-H2T.png</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-H2T.png</t>
         </is>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>H2T ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade H2T ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="P15" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -1702,64 +3230,61 @@
       <c r="Q15" s="7" t="inlineStr"/>
       <c r="R15" s="8" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>HLD-H4T</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>H4T ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="4" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>HLD-H4T.png</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-H4T.png</t>
         </is>
       </c>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>H4T ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade H4T ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -1767,64 +3292,61 @@
       <c r="Q16" s="7" t="inlineStr"/>
       <c r="R16" s="8" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="T16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>HLD-HST</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>HS-T ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>HLD-HST.png</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-HST.png</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>HS-T ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade HS-T ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -1832,125 +3354,119 @@
       <c r="Q17" s="7" t="inlineStr"/>
       <c r="R17" s="8" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="T17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18" ht="60" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>HLD-V2P</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>V2P  ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Polyvinyl Chloride (PVC)</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>HLD-V2P.png</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-V2P.png</t>
         </is>
       </c>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>V2P  ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade V2P  ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="inlineStr"/>
+      <c r="P18" s="4" t="inlineStr"/>
       <c r="Q18" s="7" t="inlineStr"/>
       <c r="R18" s="8" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="T18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19" ht="60" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>HLD-V4T</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>V4T  ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="5" t="inlineStr"/>
-      <c r="G19" s="5" t="inlineStr"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr"/>
-      <c r="J19" s="5" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>HLD-V4T.png</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-V4T.png</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>V4T  ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade V4T  ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="P19" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -1958,64 +3474,61 @@
       <c r="Q19" s="7" t="inlineStr"/>
       <c r="R19" s="8" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="T19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>HLD-VST</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>VS-T ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="5" t="inlineStr"/>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr"/>
-      <c r="J20" s="5" t="inlineStr"/>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>HLD-VST.png</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-VST.png</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>VS-T ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade VS-T ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="P20" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -2023,64 +3536,61 @@
       <c r="Q20" s="7" t="inlineStr"/>
       <c r="R20" s="8" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="T20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>HLD-EHT</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>EH-T EXECUTIVE PVC ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Executive PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>executive-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="5" t="inlineStr"/>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr"/>
-      <c r="J21" s="5" t="inlineStr"/>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>HLD-EHT.png</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-EHT.png</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>EH-T EXECUTIVE PVC ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade EH-T EXECUTIVE PVC ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Acrylic", "Orientation": "Horizontal", "Attachment Type": "Badge Clip"}</t>
         </is>
@@ -2088,64 +3598,61 @@
       <c r="Q21" s="7" t="inlineStr"/>
       <c r="R21" s="8" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="T21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="60" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>HLD-EHW</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>EH-W EXECUTIVE PLATES ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Executive PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>executive-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="F22" s="6" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>HLD-EHW.png</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-EHW.png</t>
         </is>
       </c>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>EH-W EXECUTIVE PLATES ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade EH-W EXECUTIVE PLATES ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="P22" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Horizontal", "Attachment Type": "Badge Clip"}</t>
         </is>
@@ -2153,64 +3660,61 @@
       <c r="Q22" s="7" t="inlineStr"/>
       <c r="R22" s="8" t="inlineStr"/>
       <c r="S22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="T22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>HLD-EVT</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>EV-T EXECUTIVE PVC ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Executive PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>executive-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Acrylic</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>HLD-EVT.png</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-EVT.png</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>EV-T EXECUTIVE PVC ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade EV-T EXECUTIVE PVC ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="P23" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Acrylic", "Orientation": "Vertical", "Attachment Type": "Badge Clip"}</t>
         </is>
@@ -2218,64 +3722,61 @@
       <c r="Q23" s="7" t="inlineStr"/>
       <c r="R23" s="8" t="inlineStr"/>
       <c r="S23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="T23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>HLD-EVW</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>EV-W EXECUTIVE PLATES ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Executive PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>executive-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>HLD-EVW.png</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-EVW.png</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>EV-W EXECUTIVE PLATES ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade EV-W EXECUTIVE PLATES ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="P24" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Vertical", "Attachment Type": "Badge Clip"}</t>
         </is>
@@ -2283,64 +3784,61 @@
       <c r="Q24" s="7" t="inlineStr"/>
       <c r="R24" s="8" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="T24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>HOK-LANYARDS-01</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Lanyards PLASTIC HOOK 16 mm</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="5" t="inlineStr"/>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr"/>
-      <c r="J25" s="5" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>HOK-LANYARDS-01.jpg</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-LANYARDS-01.jpg</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>Lanyards PLASTIC HOOK 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade Lanyards PLASTIC HOOK 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="P25" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Material": "Plastic", "Finish": "Steel Finish"}</t>
         </is>
@@ -2348,64 +3846,61 @@
       <c r="Q25" s="7" t="inlineStr"/>
       <c r="R25" s="8" t="inlineStr"/>
       <c r="S25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="T25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>HOK-LANYARDS-02</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>Lanyards Plastic Hook 20 Mm</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="D26" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="5" t="inlineStr"/>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Polyester Satin</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>HOK-LANYARDS-02.jpg</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-LANYARDS-02.jpg</t>
         </is>
       </c>
-      <c r="M26" s="4" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>Lanyards Plastic Hook 20 Mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade Lanyards Plastic Hook 20 Mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="P26" s="4" t="inlineStr">
         <is>
           <t>{"Plastic Type": "ABS", "Hook Type": "Hanger Hook", "Mounting Type": "Clip On"}</t>
         </is>
@@ -2413,64 +3908,61 @@
       <c r="Q26" s="7" t="inlineStr"/>
       <c r="R26" s="8" t="inlineStr"/>
       <c r="S26" s="7" t="inlineStr"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="T26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-07</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 3G 16 mm</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="5" t="inlineStr"/>
-      <c r="G27" s="5" t="inlineStr"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Plastic / Zinc Alloy</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-07.jpg</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-OVELFISH-07.jpg</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 3G 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade OVEL / FISH HOOK 3G 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="P27" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Hook Size": "3/0", "Hook Material": "High Carbon Steel"}</t>
         </is>
@@ -2478,64 +3970,61 @@
       <c r="Q27" s="7" t="inlineStr"/>
       <c r="R27" s="8" t="inlineStr"/>
       <c r="S27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="T27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-06</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 3G 20 mm</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Plastic / Zinc Alloy</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-06.jpg</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-OVELFISH-06.jpg</t>
         </is>
       </c>
-      <c r="M28" s="4" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 3G 20 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade OVEL / FISH HOOK 3G 20 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Hook Size": "3/0", "Hook Material": "High Carbon Steel"}</t>
         </is>
@@ -2543,64 +4032,61 @@
       <c r="Q28" s="7" t="inlineStr"/>
       <c r="R28" s="8" t="inlineStr"/>
       <c r="S28" s="7" t="inlineStr"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="T28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-05</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 4G 20 mm</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr"/>
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Plastic / Zinc Alloy</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-05.jpg</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-OVELFISH-05.jpg</t>
         </is>
       </c>
-      <c r="M29" s="4" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 4G 20 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade OVEL / FISH HOOK 4G 20 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Hook Size": "4/0", "Hook Material": "High Carbon Steel"}</t>
         </is>
@@ -2608,64 +4094,61 @@
       <c r="Q29" s="7" t="inlineStr"/>
       <c r="R29" s="8" t="inlineStr"/>
       <c r="S29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="T29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-03</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 5G 16 mm</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Plastic / Zinc Alloy</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr">
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-03.jpg</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-OVELFISH-03.jpg</t>
         </is>
       </c>
-      <c r="M30" s="4" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="O30" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 5G 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade OVEL / FISH HOOK 5G 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="P30" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Hook Size": "5/0", "Hook Material": "High Carbon Steel"}</t>
         </is>
@@ -2673,64 +4156,61 @@
       <c r="Q30" s="7" t="inlineStr"/>
       <c r="R30" s="8" t="inlineStr"/>
       <c r="S30" s="7" t="inlineStr"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="T30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-04</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 5G 16 mm</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="5" t="inlineStr"/>
-      <c r="G31" s="5" t="inlineStr"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
         <is>
           <t>Plastic / Zinc Alloy</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
-      <c r="K31" s="4" t="inlineStr">
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>HOK-OVELFISH-04.jpg</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-OVELFISH-04.jpg</t>
         </is>
       </c>
-      <c r="M31" s="4" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>OVEL / FISH HOOK 5G 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade OVEL / FISH HOOK 5G 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Hook Size": "5/0", "Hook Material": "High Carbon Steel"}</t>
         </is>
@@ -2738,64 +4218,61 @@
       <c r="Q31" s="7" t="inlineStr"/>
       <c r="R31" s="8" t="inlineStr"/>
       <c r="S31" s="7" t="inlineStr"/>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="T31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>HOK-SIDELEVE-09</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>SIDE LEVER / DOG HOOK 16 mm</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="5" t="inlineStr"/>
-      <c r="G32" s="5" t="inlineStr"/>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
         <is>
           <t>Stainless Steel</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr">
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>HOK-SIDELEVE-09.jpg</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-SIDELEVE-09.jpg</t>
         </is>
       </c>
-      <c r="M32" s="4" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="O32" s="4" t="inlineStr">
         <is>
           <t>SIDE LEVER / DOG HOOK 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade SIDE LEVER / DOG HOOK 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="inlineStr">
+      <c r="P32" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "Snap Hook", "Material": "Stainless Steel"}</t>
         </is>
@@ -2803,64 +4280,61 @@
       <c r="Q32" s="7" t="inlineStr"/>
       <c r="R32" s="8" t="inlineStr"/>
       <c r="S32" s="7" t="inlineStr"/>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="T32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>HOK-SIDELEVE-08</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>SIDE LEVER / DOG HOOK 20 mm</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="5" t="inlineStr"/>
-      <c r="G33" s="5" t="inlineStr"/>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>Stainless Steel</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr">
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>HOK-SIDELEVE-08.jpg</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-SIDELEVE-08.jpg</t>
         </is>
       </c>
-      <c r="M33" s="4" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="O33" s="4" t="inlineStr">
         <is>
           <t>SIDE LEVER / DOG HOOK 20 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade SIDE LEVER / DOG HOOK 20 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="P33" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "Snap Hook", "Material": "Stainless Steel", "Wire Diameter": "4 mm"}</t>
         </is>
@@ -2868,64 +4342,61 @@
       <c r="Q33" s="7" t="inlineStr"/>
       <c r="R33" s="8" t="inlineStr"/>
       <c r="S33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="T33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>HOK-TWISTHOO-13</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>TWIST HOOK 16 mm</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="5" t="inlineStr"/>
-      <c r="G34" s="5" t="inlineStr"/>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Stainless Steel</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr"/>
-      <c r="J34" s="5" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>HOK-TWISTHOO-13.jpg</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-TWISTHOO-13.jpg</t>
         </is>
       </c>
-      <c r="M34" s="4" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>TWIST HOOK 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade TWIST HOOK 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Material": "Stainless Steel", "Finish": "Steel Finish"}</t>
         </is>
@@ -2933,64 +4404,61 @@
       <c r="Q34" s="7" t="inlineStr"/>
       <c r="R34" s="8" t="inlineStr"/>
       <c r="S34" s="7" t="inlineStr"/>
-    </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="T34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>HOK-TWISTHOO-12</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>TWIST HOOK 20 mm</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="5" t="inlineStr"/>
-      <c r="G35" s="5" t="inlineStr"/>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
         <is>
           <t>Stainless Steel</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr"/>
-      <c r="J35" s="5" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr">
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>HOK-TWISTHOO-12.jpg</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="M35" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-TWISTHOO-12.jpg</t>
         </is>
       </c>
-      <c r="M35" s="4" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="O35" s="4" t="inlineStr">
         <is>
           <t>TWIST HOOK 20 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade TWIST HOOK 20 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
         <is>
           <t>{"Hook Type": "J Hook", "Material": "Stainless Steel", "Finish": "Steel Finish"}</t>
         </is>
@@ -2998,64 +4466,61 @@
       <c r="Q35" s="7" t="inlineStr"/>
       <c r="R35" s="8" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr"/>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="T35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>HOK-WIREHOOK-10</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>WIRE HOOK 12 mm</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="5" t="inlineStr"/>
-      <c r="G36" s="5" t="inlineStr"/>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
         <is>
           <t>Spring Steel</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr"/>
-      <c r="J36" s="5" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr">
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>HOK-WIREHOOK-10.jpg</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-WIREHOOK-10.jpg</t>
         </is>
       </c>
-      <c r="M36" s="4" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="O36" s="4" t="inlineStr">
         <is>
           <t>WIRE HOOK 12 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade WIRE HOOK 12 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t>{"Wire Diameter": "1.6 mm", "Material": "Spring Steel", "Hook Shape": "U Hook"}</t>
         </is>
@@ -3063,64 +4528,61 @@
       <c r="Q36" s="7" t="inlineStr"/>
       <c r="R36" s="8" t="inlineStr"/>
       <c r="S36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="T36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>HOK-WIREHOOK-11</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>WIRE HOOK 16 mm</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="5" t="inlineStr"/>
-      <c r="G37" s="5" t="inlineStr"/>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr"/>
+      <c r="I37" s="4" t="inlineStr">
         <is>
           <t>Spring Steel</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr"/>
-      <c r="J37" s="5" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr">
+      <c r="J37" s="4" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>HOK-WIREHOOK-11.jpg</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="M37" s="4" t="inlineStr">
         <is>
           <t>/media/products/HOK-WIREHOOK-11.jpg</t>
         </is>
       </c>
-      <c r="M37" s="4" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="O37" s="4" t="inlineStr">
         <is>
           <t>WIRE HOOK 16 mm - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade WIRE HOOK 16 mm manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="P37" s="4" t="inlineStr">
         <is>
           <t>{"Wire Diameter": "1.6 mm", "Material": "Spring Steel", "Hook Shape": "U Hook"}</t>
         </is>
@@ -3128,80 +4590,77 @@
       <c r="Q37" s="7" t="inlineStr"/>
       <c r="R37" s="8" t="inlineStr"/>
       <c r="S37" s="7" t="inlineStr"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="T37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT150</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>DCT150 A4+ PVC Card Making Fusing Machine</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>ID Card Manufacturing Machines</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>id-card-manufacturing-machines</t>
         </is>
       </c>
-      <c r="E38" s="6" t="n">
+      <c r="F38" s="6" t="n">
         <v>48000</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>₹ 48,000 / Piece</t>
         </is>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="H38" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Dual Aluminum Heating Plates with Water Cooling</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="4" t="inlineStr">
         <is>
           <t>Platen size: 210 x 297 mm (A4+)</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="4" t="inlineStr">
         <is>
           <t>Silver &amp; Black</t>
         </is>
       </c>
-      <c r="K38" s="4" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT150.png</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="4" t="inlineStr">
         <is>
           <t>/media/products/MCH-DCT150.png</t>
         </is>
       </c>
-      <c r="M38" s="4" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="O38" s="4" t="inlineStr">
         <is>
           <t>DCT150 A4+ PVC Card Making Fusing Machine - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
-        <is>
-          <t>High-pressure thermal fusing machine engineered for laminating multi-layer PVC printed sheets with magnetic stripes and contactless RFID inlays.</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr">
+      <c r="P38" s="4" t="inlineStr">
         <is>
           <t>{"Lamination Size": "A4+ (Up to 10 cards per sheet)", "Temperature Range": "0 - 180\u00b0C Digital Control", "Cooling System": "Circulating Water Cooling Tower", "Pressure Mode": "Manual Hydraulic Lever", "Output": "Up to 400 cards/hour"}</t>
         </is>
@@ -3209,80 +4668,77 @@
       <c r="Q38" s="7" t="inlineStr"/>
       <c r="R38" s="8" t="inlineStr"/>
       <c r="S38" s="7" t="inlineStr"/>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="T38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT2000</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>DCT2000 Semi-Automatic Double Die ID Card Cutter</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>ID Card Manufacturing Machines</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>id-card-manufacturing-machines</t>
         </is>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="F39" s="6" t="n">
         <v>65000</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>₹ 65,000 / Piece</t>
         </is>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="H39" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
+      <c r="I39" s="4" t="inlineStr">
         <is>
           <t>Tool Steel Die &amp; Mild Steel Frame</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>CR-80 Standard (85.6 x 54 mm)</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="4" t="inlineStr">
         <is>
           <t>Blue &amp; Grey</t>
         </is>
       </c>
-      <c r="K39" s="4" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT2000.png</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="4" t="inlineStr">
         <is>
           <t>/media/products/MCH-DCT2000.png</t>
         </is>
       </c>
-      <c r="M39" s="4" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="O39" s="4" t="inlineStr">
         <is>
           <t>DCT2000 Semi-Automatic Double Die ID Card Cutter - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
-        <is>
-          <t>Semi-automatic motorized double die card cutter offering up to 2,000 cards per hour with precision dual-cavity cutting dies for medium-scale printing facilities.</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="P39" s="4" t="inlineStr">
         <is>
           <t>{"Punching Capacity": "Up to 2,000 cards/hour", "Die Type": "Double Die (2 cards per stroke)", "Operation": "Foot Pedal / Push Button Electric", "Power": "220V, 50Hz, 750W", "Card Output": "Smooth burr-free rounded edges CR-80"}</t>
         </is>
@@ -3290,80 +4746,77 @@
       <c r="Q39" s="7" t="inlineStr"/>
       <c r="R39" s="8" t="inlineStr"/>
       <c r="S39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="T39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT450</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>DCT450 Continuous Roll Lanyard Print Heat Press Machine</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>ID Card Manufacturing Machines</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>id-card-manufacturing-machines</t>
         </is>
       </c>
-      <c r="E40" s="6" t="n">
+      <c r="F40" s="6" t="n">
         <v>125000</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>₹ 1,25,000 / Piece</t>
         </is>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="H40" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="I40" s="4" t="inlineStr">
         <is>
           <t>Hard Chrome Plated Heated Drum</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Drum Width: 450 mm</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="4" t="inlineStr">
         <is>
           <t>Industrial Orange &amp; Navy</t>
         </is>
       </c>
-      <c r="K40" s="4" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT450.png</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="4" t="inlineStr">
         <is>
           <t>/media/products/MCH-DCT450.png</t>
         </is>
       </c>
-      <c r="M40" s="4" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="O40" s="4" t="inlineStr">
         <is>
           <t>DCT450 Continuous Roll Lanyard Print Heat Press Machine - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
-        <is>
-          <t>Rotary calendar continuous heat transfer machine engineered for digital sublimation printing on polyester and satin lanyard rolls at variable production speeds.</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="P40" s="4" t="inlineStr">
         <is>
           <t>{"Max Web Width": "450 mm (multiple ribbons simultaneously)", "Temperature Control": "PID Solid State Digital", "Speed": "1 - 5 meters/minute adjustable", "Power": "4.5 kW 220V", "Applicable Ribbon": "12mm, 16mm, 20mm, 25mm Satin"}</t>
         </is>
@@ -3371,80 +4824,77 @@
       <c r="Q40" s="7" t="inlineStr"/>
       <c r="R40" s="8" t="inlineStr"/>
       <c r="S40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="T40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41" ht="60" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT4500</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>DCT4500 Fully Automatic Smart ID Card Cutting Machine</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>ID Card Manufacturing Machines</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>id-card-manufacturing-machines</t>
         </is>
       </c>
-      <c r="E41" s="6" t="n">
+      <c r="F41" s="6" t="n">
         <v>185000</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
         <is>
           <t>₹ 1,85,000 / Piece</t>
         </is>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="H41" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="4" t="inlineStr">
         <is>
           <t>Heavy Duty Cast Iron &amp; Alloy Steel</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="4" t="inlineStr">
         <is>
           <t>CR-80 Standard Card Size (85.6 x 54 mm)</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="4" t="inlineStr">
         <is>
           <t>Industrial Blue &amp; White</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>MCH-DCT4500.png</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="4" t="inlineStr">
         <is>
           <t>/media/products/MCH-DCT4500.png</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="O41" s="4" t="inlineStr">
         <is>
           <t>DCT4500 Fully Automatic Smart ID Card Cutting Machine - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
-        <is>
-          <t>Professional fully automatic smart card punching unit designed for high-capacity industrial production up to 4,500 ISO standard CR-80 cards per hour with optical sensor alignment.</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="P41" s="4" t="inlineStr">
         <is>
           <t>{"Punching Capacity": "Up to 4,500 cards/hour", "Card Standard": "ISO CR-80 (85.6 mm x 54 mm)", "Sheet Size": "A4, A4+, and custom sheet formats", "Power Source": "220V Single Phase Electric", "Motor Power": "1.5 kW", "Automation Grade": "Fully Automatic", "Weight": "approx. 180 kg"}</t>
         </is>
@@ -3452,64 +4902,61 @@
       <c r="Q41" s="7" t="inlineStr"/>
       <c r="R41" s="8" t="inlineStr"/>
       <c r="S41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="T41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="60" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>CLP-D16MMCLA-04</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>D- 16MM CLAMP FOR LANYARDS</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="5" t="inlineStr"/>
-      <c r="G42" s="5" t="inlineStr"/>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr">
         <is>
           <t>Satin</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr"/>
-      <c r="J42" s="5" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr">
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="5" t="inlineStr">
         <is>
           <t>CLP-D16MMCLA-04.jpg</t>
         </is>
       </c>
-      <c r="L42" s="5" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>/media/products/CLP-D16MMCLA-04.jpg</t>
         </is>
       </c>
-      <c r="M42" s="4" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="O42" s="4" t="inlineStr">
         <is>
           <t>D- 16MM CLAMP FOR LANYARDS - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade D- 16MM CLAMP FOR LANYARDS manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr">
+      <c r="P42" s="4" t="inlineStr">
         <is>
           <t>{"Lanyard Style": "Plain", "Width": "16 mm", "Material": "Satin"}</t>
         </is>
@@ -3517,64 +4964,61 @@
       <c r="Q42" s="7" t="inlineStr"/>
       <c r="R42" s="8" t="inlineStr"/>
       <c r="S42" s="7" t="inlineStr"/>
-    </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="T42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>CLP-D20MMCLA-05</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>D- 20MM CLAMP FOR LANYARDS</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="5" t="inlineStr"/>
-      <c r="G43" s="5" t="inlineStr"/>
-      <c r="H43" s="5" t="inlineStr">
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr">
         <is>
           <t>Satin</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr"/>
-      <c r="J43" s="5" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr">
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="5" t="inlineStr">
         <is>
           <t>CLP-D20MMCLA-05.jpg</t>
         </is>
       </c>
-      <c r="L43" s="5" t="inlineStr">
+      <c r="M43" s="4" t="inlineStr">
         <is>
           <t>/media/products/CLP-D20MMCLA-05.jpg</t>
         </is>
       </c>
-      <c r="M43" s="4" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="O43" s="4" t="inlineStr">
         <is>
           <t>D- 20MM CLAMP FOR LANYARDS - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade D- 20MM CLAMP FOR LANYARDS manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="P43" s="4" t="inlineStr">
         <is>
           <t>{"Lanyard Style": "Plain", "Width": "20 mm", "Material": "Satin"}</t>
         </is>
@@ -3582,64 +5026,61 @@
       <c r="Q43" s="7" t="inlineStr"/>
       <c r="R43" s="8" t="inlineStr"/>
       <c r="S43" s="7" t="inlineStr"/>
-    </row>
-    <row r="44" ht="20" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="T43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>CLP-M12MMCLA-02</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>M- 12MM CLAMP FOR LANYARDS</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="5" t="inlineStr"/>
-      <c r="G44" s="5" t="inlineStr"/>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr">
         <is>
           <t>Polyester Satin</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr"/>
-      <c r="J44" s="5" t="inlineStr"/>
-      <c r="K44" s="4" t="inlineStr">
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="5" t="inlineStr">
         <is>
           <t>CLP-M12MMCLA-02.jpg</t>
         </is>
       </c>
-      <c r="L44" s="5" t="inlineStr">
+      <c r="M44" s="4" t="inlineStr">
         <is>
           <t>/media/products/CLP-M12MMCLA-02.jpg</t>
         </is>
       </c>
-      <c r="M44" s="4" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="O44" s="4" t="inlineStr">
         <is>
           <t>M- 12MM CLAMP FOR LANYARDS - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade M- 12MM CLAMP FOR LANYARDS manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="P44" s="4" t="inlineStr">
         <is>
           <t>{"Material Grade": "Mild Steel", "Clamp Type": "C Clamp", "Grating Size Suitability": "20\u201325 mm"}</t>
         </is>
@@ -3647,64 +5088,61 @@
       <c r="Q44" s="7" t="inlineStr"/>
       <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="7" t="inlineStr"/>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="T44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="4" t="inlineStr"/>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>CLP-M20MMCLA-03</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>M- 20MM CLAMP FOR LANYARDS</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="D45" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr"/>
-      <c r="F45" s="5" t="inlineStr"/>
-      <c r="G45" s="5" t="inlineStr"/>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr">
         <is>
           <t>Polyester Satin</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr"/>
-      <c r="J45" s="5" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr">
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="5" t="inlineStr">
         <is>
           <t>CLP-M20MMCLA-03.jpg</t>
         </is>
       </c>
-      <c r="L45" s="5" t="inlineStr">
+      <c r="M45" s="4" t="inlineStr">
         <is>
           <t>/media/products/CLP-M20MMCLA-03.jpg</t>
         </is>
       </c>
-      <c r="M45" s="4" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="O45" s="4" t="inlineStr">
         <is>
           <t>M- 20MM CLAMP FOR LANYARDS - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade M- 20MM CLAMP FOR LANYARDS manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="P45" s="4" t="inlineStr">
         <is>
           <t>{"Material Grade": "Mild Steel", "Clamp Type": "C Clamp", "Grating Size Suitability": "20\u201325 mm"}</t>
         </is>
@@ -3712,64 +5150,61 @@
       <c r="Q45" s="7" t="inlineStr"/>
       <c r="R45" s="8" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr"/>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="T45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46" ht="60" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>CLP-M16MM</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>M-16MM CLAMP FOR LANYARDS</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="D46" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="D46" s="4" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr"/>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr">
         <is>
           <t>Metal</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr"/>
-      <c r="J46" s="5" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr">
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="5" t="inlineStr">
         <is>
           <t>CLP-M16MM.jpg</t>
         </is>
       </c>
-      <c r="L46" s="5" t="inlineStr">
+      <c r="M46" s="4" t="inlineStr">
         <is>
           <t>/media/products/CLP-M16MM.jpg</t>
         </is>
       </c>
-      <c r="M46" s="4" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="O46" s="4" t="inlineStr">
         <is>
           <t>M-16MM CLAMP FOR LANYARDS - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade M-16MM CLAMP FOR LANYARDS manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="inlineStr">
+      <c r="P46" s="4" t="inlineStr">
         <is>
           <t>{"Accessory Type": "Clip", "Material": "Metal", "Finish": "Chrome Plated"}</t>
         </is>
@@ -3777,64 +5212,61 @@
       <c r="Q46" s="7" t="inlineStr"/>
       <c r="R46" s="8" t="inlineStr"/>
       <c r="S46" s="7" t="inlineStr"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="T46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="4" t="inlineStr"/>
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>HLD-HS</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>HS ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>PVC ID Card Sticker Pasting Holder</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>pvc-id-card-sticker-pasting-holder</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr"/>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr"/>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr"/>
-      <c r="J47" s="5" t="inlineStr"/>
-      <c r="K47" s="4" t="inlineStr">
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="5" t="inlineStr">
         <is>
           <t>HLD-HS.png</t>
         </is>
       </c>
-      <c r="L47" s="5" t="inlineStr">
+      <c r="M47" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-HS.png</t>
         </is>
       </c>
-      <c r="M47" s="4" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="O47" s="4" t="inlineStr">
         <is>
           <t>HS ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade HS ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="P47" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Horizontal"}</t>
         </is>
@@ -3842,64 +5274,61 @@
       <c r="Q47" s="7" t="inlineStr"/>
       <c r="R47" s="8" t="inlineStr"/>
       <c r="S47" s="7" t="inlineStr"/>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="T47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>HLD-HS2</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>HS2 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>PVC ID Card Sticker Pasting Holder</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>pvc-id-card-sticker-pasting-holder</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr"/>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr"/>
-      <c r="J48" s="5" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr">
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="5" t="inlineStr">
         <is>
           <t>HLD-HS2.png</t>
         </is>
       </c>
-      <c r="L48" s="5" t="inlineStr">
+      <c r="M48" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-HS2.png</t>
         </is>
       </c>
-      <c r="M48" s="4" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="O48" s="4" t="inlineStr">
         <is>
           <t>HS2 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade HS2 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="inlineStr">
+      <c r="P48" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -3907,64 +5336,61 @@
       <c r="Q48" s="7" t="inlineStr"/>
       <c r="R48" s="8" t="inlineStr"/>
       <c r="S48" s="7" t="inlineStr"/>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="T48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>HLD-VS</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>VS ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>PVC ID Card Sticker Pasting Holder</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>pvc-id-card-sticker-pasting-holder</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr"/>
-      <c r="F49" s="5" t="inlineStr"/>
-      <c r="G49" s="5" t="inlineStr"/>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr"/>
-      <c r="J49" s="5" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr">
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="5" t="inlineStr">
         <is>
           <t>HLD-VS.png</t>
         </is>
       </c>
-      <c r="L49" s="5" t="inlineStr">
+      <c r="M49" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-VS.png</t>
         </is>
       </c>
-      <c r="M49" s="4" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="O49" s="4" t="inlineStr">
         <is>
           <t>VS ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade VS ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="P49" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -3972,64 +5398,61 @@
       <c r="Q49" s="7" t="inlineStr"/>
       <c r="R49" s="8" t="inlineStr"/>
       <c r="S49" s="7" t="inlineStr"/>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="T49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>HLD-VS2</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>VS2 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>PVC ID Card Sticker Pasting Holder</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>pvc-id-card-sticker-pasting-holder</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr"/>
-      <c r="F50" s="5" t="inlineStr"/>
-      <c r="G50" s="5" t="inlineStr"/>
-      <c r="H50" s="5" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr"/>
-      <c r="J50" s="5" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr">
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="5" t="inlineStr">
         <is>
           <t>HLD-VS2.png</t>
         </is>
       </c>
-      <c r="L50" s="5" t="inlineStr">
+      <c r="M50" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-VS2.png</t>
         </is>
       </c>
-      <c r="M50" s="4" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="O50" s="4" t="inlineStr">
         <is>
           <t>VS2 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade VS2 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="inlineStr">
+      <c r="P50" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Vertical"}</t>
         </is>
@@ -4037,80 +5460,77 @@
       <c r="Q50" s="7" t="inlineStr"/>
       <c r="R50" s="8" t="inlineStr"/>
       <c r="S50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="T50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>CNS-PVCA4-50</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>A4 Inkjet Printable PVC Core Sheet Sets (3-Layer Kit)</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>RFID Smart Cards &amp; Consumables</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>rfid-smart-cards-and-consumables</t>
         </is>
       </c>
-      <c r="E51" s="6" t="n">
+      <c r="F51" s="6" t="n">
         <v>1450</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>₹ 1,450 / Pack of 50 Sets</t>
         </is>
       </c>
-      <c r="G51" s="5" t="n">
+      <c r="H51" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="I51" s="4" t="inlineStr">
         <is>
           <t>Polyvinyl Chloride (PVC)</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="4" t="inlineStr">
         <is>
           <t>200 mm x 300 mm (A4 Format)</t>
         </is>
       </c>
-      <c r="J51" s="5" t="inlineStr">
+      <c r="K51" s="4" t="inlineStr">
         <is>
           <t>Opaque White Core + Clear Overlays</t>
         </is>
       </c>
-      <c r="K51" s="4" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr">
         <is>
           <t>CNS-PVCA4-50.png</t>
         </is>
       </c>
-      <c r="L51" s="5" t="inlineStr">
+      <c r="M51" s="4" t="inlineStr">
         <is>
           <t>/media/products/CNS-PVCA4-50.png</t>
         </is>
       </c>
-      <c r="M51" s="4" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="O51" s="4" t="inlineStr">
         <is>
           <t>A4 Inkjet Printable PVC Core Sheet Sets (3-Layer Kit) - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
-        <is>
-          <t>Professional 3-layer digital PVC card making sheet pack (2 printable film sheets + 1 middle core sheet) producing 10 waterproof high-resolution credit-card-thick ID badges per sheet.</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="P51" s="4" t="inlineStr">
         <is>
           <t>{"Total Thickness": "0.76 mm standard ISO thickness", "Core Thickness": "0.46 mm white PVC core", "Overlay Thickness": "0.15 mm transparent printable film (2 sides)", "Printing Tech": "Epson / Canon standard dye and pigment inkjet printers", "Quantity per Pack": "50 sets (Yields 500 ID cards)"}</t>
         </is>
@@ -4118,80 +5538,77 @@
       <c r="Q51" s="7" t="inlineStr"/>
       <c r="R51" s="8" t="inlineStr"/>
       <c r="S51" s="7" t="inlineStr"/>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="T51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>CRD-EM4100-WHT</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>EM4100 125KHz Proximity RFID Clamshell &amp; Thin Cards</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>RFID Smart Cards &amp; Consumables</t>
         </is>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>rfid-smart-cards-and-consumables</t>
         </is>
       </c>
-      <c r="E52" s="6" t="n">
+      <c r="F52" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>₹ 12 / Piece</t>
         </is>
       </c>
-      <c r="G52" s="5" t="n">
+      <c r="H52" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="I52" s="4" t="inlineStr">
         <is>
           <t>PVC / ABS Core</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>85.6 mm x 54 mm x 0.8 mm (Thin) / 1.8 mm (Clamshell)</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="K52" s="4" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="K52" s="4" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr">
         <is>
           <t>CRD-EM4100-WHT.png</t>
         </is>
       </c>
-      <c r="L52" s="5" t="inlineStr">
+      <c r="M52" s="4" t="inlineStr">
         <is>
           <t>/media/products/CRD-EM4100-WHT.png</t>
         </is>
       </c>
-      <c r="M52" s="4" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="O52" s="4" t="inlineStr">
         <is>
           <t>EM4100 125KHz Proximity RFID Clamshell &amp; Thin Cards - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
-        <is>
-          <t>Low-frequency 125KHz read-only proximity cards with pre-programmed unique 64-bit ID code for electronic door access, parking systems, and time attendance clocks.</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr">
+      <c r="P52" s="4" t="inlineStr">
         <is>
           <t>{"Frequency": "125 KHz LF", "Chipset": "EM4100 / TK4100 Compatible", "Encoding": "64-bit Manchester", "Read Range": "5 - 12 cm", "Durability": "Waterproof and dustproof hermetic seal"}</t>
         </is>
@@ -4199,80 +5616,77 @@
       <c r="Q52" s="7" t="inlineStr"/>
       <c r="R52" s="8" t="inlineStr"/>
       <c r="S52" s="7" t="inlineStr"/>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="T52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>CRD-MF1K-WHT</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Mifare 1K Classic RFID ISO Smart Cards</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>RFID Smart Cards &amp; Consumables</t>
         </is>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>rfid-smart-cards-and-consumables</t>
         </is>
       </c>
-      <c r="E53" s="6" t="n">
+      <c r="F53" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>₹ 18 / Piece</t>
         </is>
       </c>
-      <c r="G53" s="5" t="n">
+      <c r="H53" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="I53" s="4" t="inlineStr">
         <is>
           <t>Premium Laminated PVC</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>85.6 mm x 54 mm x 0.84 mm (CR-80)</t>
         </is>
       </c>
-      <c r="J53" s="5" t="inlineStr">
+      <c r="K53" s="4" t="inlineStr">
         <is>
           <t>Glossy White Printable</t>
         </is>
       </c>
-      <c r="K53" s="4" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr">
         <is>
           <t>CRD-MF1K-WHT.png</t>
         </is>
       </c>
-      <c r="L53" s="5" t="inlineStr">
+      <c r="M53" s="4" t="inlineStr">
         <is>
           <t>/media/products/CRD-MF1K-WHT.png</t>
         </is>
       </c>
-      <c r="M53" s="4" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="O53" s="4" t="inlineStr">
         <is>
           <t>Mifare 1K Classic RFID ISO Smart Cards - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
-        <is>
-          <t>Standard 13.56MHz ISO/IEC 14443 Type A contactless smart cards featuring 1024 bytes EEPROM, 16 sectors with independent access keys, suitable for access control and campus transit.</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr">
+      <c r="P53" s="4" t="inlineStr">
         <is>
           <t>{"Operating Frequency": "13.56 MHz High Frequency", "Chip Protocol": "ISO 14443A Mifare Classic 1K Compatible", "Memory": "1 KB EEPROM (16 sectors)", "Read Distance": "Up to 10 cm", "Surface Finish": "Glossy / Inkjet &amp; Thermal printable", "Operating Temperature": "-20\u00b0C to +50\u00b0C"}</t>
         </is>
@@ -4280,64 +5694,61 @@
       <c r="Q53" s="7" t="inlineStr"/>
       <c r="R53" s="8" t="inlineStr"/>
       <c r="S53" s="7" t="inlineStr"/>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="T53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>HLD-C2</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>C2 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E54" s="6" t="inlineStr"/>
-      <c r="F54" s="5" t="inlineStr"/>
-      <c r="G54" s="5" t="inlineStr"/>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
         <is>
           <t>Polyvinyl Chloride (PVC)</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr"/>
-      <c r="J54" s="5" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr">
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="5" t="inlineStr">
         <is>
           <t>HLD-C2.png</t>
         </is>
       </c>
-      <c r="L54" s="5" t="inlineStr">
+      <c r="M54" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-C2.png</t>
         </is>
       </c>
-      <c r="M54" s="4" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="O54" s="4" t="inlineStr">
         <is>
           <t>C2 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade C2 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr">
+      <c r="P54" s="4" t="inlineStr">
         <is>
           <t>{"Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4345,64 +5756,61 @@
       <c r="Q54" s="7" t="inlineStr"/>
       <c r="R54" s="8" t="inlineStr"/>
       <c r="S54" s="7" t="inlineStr"/>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="T54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>HLD-H2</t>
         </is>
       </c>
-      <c r="B55" s="5" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>H2 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D55" s="4" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E55" s="6" t="inlineStr"/>
-      <c r="F55" s="5" t="inlineStr"/>
-      <c r="G55" s="5" t="inlineStr"/>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="5" t="inlineStr"/>
-      <c r="K55" s="4" t="inlineStr">
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
         <is>
           <t>HLD-H2.png</t>
         </is>
       </c>
-      <c r="L55" s="5" t="inlineStr">
+      <c r="M55" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-H2.png</t>
         </is>
       </c>
-      <c r="M55" s="4" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="O55" s="4" t="inlineStr">
         <is>
           <t>H2 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade H2 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="P55" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Horizontal"}</t>
         </is>
@@ -4410,64 +5818,61 @@
       <c r="Q55" s="7" t="inlineStr"/>
       <c r="R55" s="8" t="inlineStr"/>
       <c r="S55" s="7" t="inlineStr"/>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="T55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>HLD-H2H</t>
         </is>
       </c>
-      <c r="B56" s="5" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>H2H ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E56" s="6" t="inlineStr"/>
-      <c r="F56" s="5" t="inlineStr"/>
-      <c r="G56" s="5" t="inlineStr"/>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I56" s="5" t="inlineStr"/>
-      <c r="J56" s="5" t="inlineStr"/>
-      <c r="K56" s="4" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="5" t="inlineStr">
         <is>
           <t>HLD-H2H.png</t>
         </is>
       </c>
-      <c r="L56" s="5" t="inlineStr">
+      <c r="M56" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-H2H.png</t>
         </is>
       </c>
-      <c r="M56" s="4" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="O56" s="4" t="inlineStr">
         <is>
           <t>H2H ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade H2H ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P56" s="5" t="inlineStr">
+      <c r="P56" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4475,64 +5880,61 @@
       <c r="Q56" s="7" t="inlineStr"/>
       <c r="R56" s="8" t="inlineStr"/>
       <c r="S56" s="7" t="inlineStr"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="T56" s="7" t="inlineStr"/>
+    </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>HLD-H4</t>
         </is>
       </c>
-      <c r="B57" s="5" t="inlineStr">
+      <c r="C57" s="4" t="inlineStr">
         <is>
           <t>H4 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C57" s="5" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="E57" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr"/>
-      <c r="F57" s="5" t="inlineStr"/>
-      <c r="G57" s="5" t="inlineStr"/>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr">
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="5" t="inlineStr">
         <is>
           <t>HLD-H4.png</t>
         </is>
       </c>
-      <c r="L57" s="5" t="inlineStr">
+      <c r="M57" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-H4.png</t>
         </is>
       </c>
-      <c r="M57" s="4" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="O57" s="4" t="inlineStr">
         <is>
           <t>H4 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade H4 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="P57" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Horizontal", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4540,64 +5942,61 @@
       <c r="Q57" s="7" t="inlineStr"/>
       <c r="R57" s="8" t="inlineStr"/>
       <c r="S57" s="7" t="inlineStr"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="T57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58" ht="60" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>HLD-V2</t>
         </is>
       </c>
-      <c r="B58" s="5" t="inlineStr">
+      <c r="C58" s="4" t="inlineStr">
         <is>
           <t>V2 ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E58" s="6" t="inlineStr"/>
-      <c r="F58" s="5" t="inlineStr"/>
-      <c r="G58" s="5" t="inlineStr"/>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
-      <c r="K58" s="4" t="inlineStr">
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="5" t="inlineStr">
         <is>
           <t>HLD-V2.png</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="M58" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-V2.png</t>
         </is>
       </c>
-      <c r="M58" s="4" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="O58" s="4" t="inlineStr">
         <is>
           <t>V2 ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade V2 ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="inlineStr">
+      <c r="P58" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4605,64 +6004,61 @@
       <c r="Q58" s="7" t="inlineStr"/>
       <c r="R58" s="8" t="inlineStr"/>
       <c r="S58" s="7" t="inlineStr"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="T58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>HLD-V2H</t>
         </is>
       </c>
-      <c r="B59" s="5" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>V2H ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E59" s="6" t="inlineStr"/>
-      <c r="F59" s="5" t="inlineStr"/>
-      <c r="G59" s="5" t="inlineStr"/>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr">
         <is>
           <t>Plastic</t>
         </is>
       </c>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr">
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>HLD-V2H.png</t>
         </is>
       </c>
-      <c r="L59" s="5" t="inlineStr">
+      <c r="M59" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-V2H.png</t>
         </is>
       </c>
-      <c r="M59" s="4" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="O59" s="4" t="inlineStr">
         <is>
           <t>V2H ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade V2H ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="P59" s="4" t="inlineStr">
         <is>
           <t>{"Material": "Plastic", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4670,64 +6066,61 @@
       <c r="Q59" s="7" t="inlineStr"/>
       <c r="R59" s="8" t="inlineStr"/>
       <c r="S59" s="7" t="inlineStr"/>
-    </row>
-    <row r="60" ht="20" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="T59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>HLD-V4</t>
         </is>
       </c>
-      <c r="B60" s="5" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>V4  ID CARD HOLDER</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="E60" s="6" t="inlineStr"/>
-      <c r="F60" s="5" t="inlineStr"/>
-      <c r="G60" s="5" t="inlineStr"/>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr">
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="5" t="inlineStr">
         <is>
           <t>HLD-V4.png</t>
         </is>
       </c>
-      <c r="L60" s="5" t="inlineStr">
+      <c r="M60" s="4" t="inlineStr">
         <is>
           <t>/media/products/HLD-V4.png</t>
         </is>
       </c>
-      <c r="M60" s="4" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="O60" s="4" t="inlineStr">
         <is>
           <t>V4  ID CARD HOLDER - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade V4  ID CARD HOLDER manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="P60" s="4" t="inlineStr">
         <is>
           <t>{"Material": "PVC", "Orientation": "Vertical", "Attachment Type": "Lanyard Slot"}</t>
         </is>
@@ -4735,68 +6128,65 @@
       <c r="Q60" s="7" t="inlineStr"/>
       <c r="R60" s="8" t="inlineStr"/>
       <c r="S60" s="7" t="inlineStr"/>
-    </row>
-    <row r="61" ht="20" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="T60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61" ht="60" customHeight="1">
+      <c r="A61" s="4" t="inlineStr"/>
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-16M</t>
         </is>
       </c>
-      <c r="B61" s="5" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>16MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>White Satin Digital Lanyard Roll</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>white-satin-digital-lanyard-roll</t>
         </is>
       </c>
-      <c r="E61" s="6" t="inlineStr"/>
-      <c r="F61" s="5" t="inlineStr"/>
-      <c r="G61" s="5" t="inlineStr"/>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
+      <c r="H61" s="4" t="inlineStr"/>
+      <c r="I61" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr">
+      <c r="J61" s="4" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="K61" s="4" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-16M.png</t>
         </is>
       </c>
-      <c r="L61" s="5" t="inlineStr">
+      <c r="M61" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-WHI-16M.png</t>
         </is>
       </c>
-      <c r="M61" s="4" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="O61" s="4" t="inlineStr">
         <is>
           <t>16MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 16MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="P61" s="4" t="inlineStr">
         <is>
           <t>{"Ribbon Width": "16 mm", "Pack Length": "100 m", "Color": "White", "Material": "Polyester", "Side Type": "Double Face", "Usage": "id card lanyard printing", "Finish": "Semi Gloss", "Pack Type": "Roll", "Pattern": "Plain"}</t>
         </is>
@@ -4804,68 +6194,65 @@
       <c r="Q61" s="7" t="inlineStr"/>
       <c r="R61" s="8" t="inlineStr"/>
       <c r="S61" s="7" t="inlineStr"/>
-    </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="T61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
+      <c r="A62" s="4" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-20M</t>
         </is>
       </c>
-      <c r="B62" s="5" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>20 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING</t>
         </is>
       </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="D62" s="4" t="inlineStr">
         <is>
           <t>White Satin Digital Lanyard Roll</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="E62" s="5" t="inlineStr">
         <is>
           <t>white-satin-digital-lanyard-roll</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr"/>
-      <c r="F62" s="5" t="inlineStr"/>
-      <c r="G62" s="5" t="inlineStr"/>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr"/>
+      <c r="I62" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr">
+      <c r="J62" s="4" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="K62" s="4" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-20M.png</t>
         </is>
       </c>
-      <c r="L62" s="5" t="inlineStr">
+      <c r="M62" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-WHI-20M.png</t>
         </is>
       </c>
-      <c r="M62" s="4" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="O62" s="4" t="inlineStr">
         <is>
           <t>20 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 20 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P62" s="5" t="inlineStr">
+      <c r="P62" s="4" t="inlineStr">
         <is>
           <t>{"Ribbon Width": "20", "Width": "20", "Pack Length": "100 m", "Length Per Roll": "100 m", "Color": "White", "Material": "Polyester", "Weave Type": "Single Face", "Side Type": "Single Face", "Thickness": "0.15 mm", "Usage": "Packaging", "Finish": "Glossy"}</t>
         </is>
@@ -4873,68 +6260,65 @@
       <c r="Q62" s="7" t="inlineStr"/>
       <c r="R62" s="8" t="inlineStr"/>
       <c r="S62" s="7" t="inlineStr"/>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="T62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-25M</t>
         </is>
       </c>
-      <c r="B63" s="5" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>25 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>White Satin Digital Lanyard Roll</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>white-satin-digital-lanyard-roll</t>
         </is>
       </c>
-      <c r="E63" s="6" t="inlineStr"/>
-      <c r="F63" s="5" t="inlineStr"/>
-      <c r="G63" s="5" t="inlineStr"/>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr"/>
+      <c r="I63" s="4" t="inlineStr">
         <is>
           <t>Polyester</t>
         </is>
       </c>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr">
+      <c r="J63" s="4" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
         <is>
           <t>White</t>
         </is>
       </c>
-      <c r="K63" s="4" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr">
         <is>
           <t>LAN-WHI-25M.png</t>
         </is>
       </c>
-      <c r="L63" s="5" t="inlineStr">
+      <c r="M63" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-WHI-25M.png</t>
         </is>
       </c>
-      <c r="M63" s="4" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="O63" s="4" t="inlineStr">
         <is>
           <t>25 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING - Professional wholesale catalogue item.</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
-        <is>
-          <t>Industrial grade 25 MM WHITE SATIN ROLL FOR SUBLIMATION PRINTING manufactured specifically for professional ID card systems, commercial lanyards, and event identification. Offered in standard bulk packaging with verified dimensional accuracy.</t>
-        </is>
-      </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="P63" s="4" t="inlineStr">
         <is>
           <t>{"Ribbon Width": "25 mm", "Pack Length": "100 m", "Color": "White", "Material": "Polyester", "Side Type": "Double Face", "Usage": "lanyards", "Finish": "Glossy", "Pattern": "Plain", "Pack Type": "Roll"}</t>
         </is>
@@ -4942,80 +6326,77 @@
       <c r="Q63" s="7" t="inlineStr"/>
       <c r="R63" s="8" t="inlineStr"/>
       <c r="S63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="T63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
+      <c r="A64" s="4" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>LAN-SUB-20MM</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>Custom Sublimation Heat Transfer Printed Lanyards (20mm)</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="D64" s="4" t="inlineStr">
         <is>
           <t>White Satin Digital Lanyard Roll</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>white-satin-digital-lanyard-roll</t>
         </is>
       </c>
-      <c r="E64" s="6" t="n">
+      <c r="F64" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
+      <c r="G64" s="4" t="inlineStr">
         <is>
           <t>₹ 14 / Piece</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n">
+      <c r="H64" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="I64" s="4" t="inlineStr">
         <is>
           <t>Micro-weave Smooth Satin Polyester</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr">
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>20 mm Width x 900 mm Length</t>
         </is>
       </c>
-      <c r="J64" s="5" t="inlineStr">
+      <c r="K64" s="4" t="inlineStr">
         <is>
           <t>Full Color CMYK Custom Print</t>
         </is>
       </c>
-      <c r="K64" s="4" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr">
         <is>
           <t>LAN-SUB-20MM.png</t>
         </is>
       </c>
-      <c r="L64" s="5" t="inlineStr">
+      <c r="M64" s="4" t="inlineStr">
         <is>
           <t>/media/products/LAN-SUB-20MM.png</t>
         </is>
       </c>
-      <c r="M64" s="4" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="O64" s="4" t="inlineStr">
         <is>
           <t>Custom Sublimation Heat Transfer Printed Lanyards (20mm) - High performance production grade equipment.</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
-        <is>
-          <t>Full-color edge-to-edge sublimation digitally printed satin lanyards with photographic quality corporate logos, text, and gradient designs with premium dog hook attachments.</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="P64" s="4" t="inlineStr">
         <is>
           <t>{"Printing Quality": "Photographic Sublimation (No color fading)", "Strap Width": "20 mm (Also available in 16mm and 25mm)", "Fitting Included": "Deluxe Metal Dog Hook / Side Lever", "Optional Addons": "Quick release buckle, safety breakaway clip", "Washability": "100% Machine washable"}</t>
         </is>
@@ -5023,9 +6404,11 @@
       <c r="Q64" s="7" t="inlineStr"/>
       <c r="R64" s="8" t="inlineStr"/>
       <c r="S64" s="7" t="inlineStr"/>
+      <c r="T64" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5036,7 +6419,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="38" customWidth="1" min="2" max="2"/>
@@ -5079,400 +6462,262 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Color ID Card Lanyard Roll</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>color-id-card-lanyard-roll</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Semi Transparent PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>semi-transparent-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Crystal Clear PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>crystal-clear-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>ID Card Lanyard Hooks &amp; Fittings</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>id-card-lanyard-hooks</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>PVC ID Card Sticker Pasting Holder</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>pvc-id-card-sticker-pasting-holder</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Executive PVC ID Card Holder</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>executive-pvc-id-card-holder</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>White Satin Digital Lanyard Roll</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>white-satin-digital-lanyard-roll</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Lanyard Fitting Metal Clamp</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>lanyard-fitting-metal-clamp-for-id-card-lanyards</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>ID Card Manufacturing Machines</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>id-card-manufacturing-machines</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>RFID Smart Cards &amp; Consumables</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>rfid-smart-cards-and-consumables</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Active</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="95" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>THE PRINT PLANET - B2B PRODUCT CATALOG EDITING &amp; IMPORT GUIDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="11" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Dear Client,</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Attached is your complete active product catalogue (63 industrial supplies items).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>All Delta Industry supplier branding and watermarks have been removed from the images.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Every product is linked to its clean, verified high-resolution photograph.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>HOW TO EDIT AND IMPORT INTO PRODUCTION:</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>1. Review Existing Products: Check the "Products Catalog (Editable)" sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>2. Update Pricing: In column "Client Revised Price (INR)" or "Trade Price (INR)", enter your trade prices.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>3. Update Titles &amp; Descriptions: You can edit the "Product Name" or use "Client Revised Name".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
-        <is>
-          <t>4. Add New Products: You can add new rows at the bottom of the table using any of the 10 categories.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>5. Save File: Save this workbook as .xlsx or .csv.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>6. 1-Click Import: Go to your website admin portal at "/owner/import", choose this file, and click "Validate &amp; Preview" -&gt; "Execute Import".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>SUPPORT &amp; CONFIGURATION:</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>• Owner Portal: https://theprintplanet.in/owner/dashboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>• Image Media Directory: /media/products/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>• Automatic Daily Safety Backups: Enabled</t>
         </is>
       </c>
     </row>
